--- a/docs/audio_cinematics/genesis_sprachzeilen_C00-C21.xlsx
+++ b/docs/audio_cinematics/genesis_sprachzeilen_C00-C21.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$1:$S$196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$1:$S$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S196"/>
+  <dimension ref="A1:S201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9950,12 +9950,22 @@
           <t>00:01:30:00</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>00:01:04:00</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>00:01:05:17</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>1.7</v>
+      </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>zurückgestellt, Kanon-Entscheidung CON33-01 offen</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -9990,7 +10000,7 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>zurückgestellt (CON33-01); bedingt</t>
+          <t>Zeitcode vorläufig/geschätzt; bedingt</t>
         </is>
       </c>
       <c r="S107" t="inlineStr"/>
@@ -10031,12 +10041,22 @@
           <t>00:02:10:00</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>00:01:31:00</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>00:01:34:00</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>3</v>
+      </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>zurückgestellt, Kanon-Entscheidung CON33-01 offen</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -10071,7 +10091,7 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>zurückgestellt (CON33-01)</t>
+          <t>Zeitcode vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="S108" t="inlineStr"/>
@@ -10112,12 +10132,22 @@
           <t>00:02:10:00</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>00:01:36:02</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>00:01:40:00</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>3.9</v>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>zurückgestellt, Kanon-Entscheidung CON33-01 offen</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -10148,7 +10178,7 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>zurückgestellt (CON33-01)</t>
+          <t>Zeitcode vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="S109" t="inlineStr"/>
@@ -10189,12 +10219,22 @@
           <t>00:00:38:00</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>00:00:01:00</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>00:00:04:00</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>3</v>
+      </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>zurückgestellt, Kanon-Entscheidung CON33-01 offen</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -10225,7 +10265,7 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>zurückgestellt (CON33-01)</t>
+          <t>Zeitcode vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="S110" t="inlineStr"/>
@@ -10266,12 +10306,22 @@
           <t>00:00:38:00</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>00:00:06:02</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>00:00:11:07</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>5.2</v>
+      </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>zurückgestellt, Kanon-Entscheidung CON33-01 offen</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -10302,7 +10352,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>zurückgestellt (CON33-01)</t>
+          <t>Zeitcode vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="S111" t="inlineStr"/>
@@ -10343,12 +10393,22 @@
           <t>00:01:18:00</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>00:00:39:00</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>00:00:41:02</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>2.1</v>
+      </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>zurückgestellt, Kanon-Entscheidung CON33-01 offen</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -10383,7 +10443,7 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>zurückgestellt (CON33-01); bedingt</t>
+          <t>Zeitcode vorläufig/geschätzt; bedingt</t>
         </is>
       </c>
       <c r="S112" t="inlineStr"/>
@@ -10424,12 +10484,22 @@
           <t>00:01:18:00</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>00:00:41:17</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>00:00:45:02</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>3.4</v>
+      </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>zurückgestellt, Kanon-Entscheidung CON33-01 offen</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -10460,7 +10530,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>zurückgestellt (CON33-01)</t>
+          <t>Zeitcode vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="S113" t="inlineStr"/>
@@ -10501,12 +10571,22 @@
           <t>00:02:18:00</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>00:01:19:00</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>00:01:21:02</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>2.1</v>
+      </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>zurückgestellt, Kanon-Entscheidung CON33-01 offen</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -10537,7 +10617,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>zurückgestellt (CON33-01)</t>
+          <t>Zeitcode vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="S114" t="inlineStr"/>
@@ -10578,12 +10658,22 @@
           <t>00:02:18:00</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>00:01:23:05</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>00:01:25:07</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>2.1</v>
+      </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>zurückgestellt, Kanon-Entscheidung CON33-01 offen</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -10618,7 +10708,7 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>zurückgestellt (CON33-01)</t>
+          <t>Zeitcode vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="S115" t="inlineStr"/>
@@ -10659,12 +10749,22 @@
           <t>00:03:33:00</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>00:02:19:00</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>00:02:22:00</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>3</v>
+      </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>zurückgestellt, Kanon-Entscheidung CON33-01 offen</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -10695,7 +10795,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>zurückgestellt (CON33-01)</t>
+          <t>Zeitcode vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="S116" t="inlineStr"/>
@@ -10736,12 +10836,22 @@
           <t>00:03:33:00</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>00:02:22:14</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>00:02:24:07</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>1.7</v>
+      </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>zurückgestellt, Kanon-Entscheidung CON33-01 offen</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -10772,7 +10882,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>zurückgestellt (CON33-01)</t>
+          <t>Zeitcode vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="S117" t="inlineStr"/>
@@ -10813,12 +10923,22 @@
           <t>00:03:33:00</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>00:02:24:22</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>00:02:27:22</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>3</v>
+      </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>zurückgestellt, Kanon-Entscheidung CON33-01 offen</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -10849,7 +10969,7 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>zurückgestellt (CON33-01)</t>
+          <t>Zeitcode vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="S118" t="inlineStr"/>
@@ -10890,12 +11010,22 @@
           <t>00:03:33:00</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>00:02:28:12</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>00:02:32:19</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>4.3</v>
+      </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>zurückgestellt, Kanon-Entscheidung CON33-01 offen</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -10926,7 +11056,7 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>zurückgestellt (CON33-01)</t>
+          <t>Zeitcode vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="S119" t="inlineStr"/>
@@ -10967,12 +11097,22 @@
           <t>00:04:30:00</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>00:03:34:00</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>00:03:37:22</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>3.9</v>
+      </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>zurückgestellt, Kanon-Entscheidung CON33-01 offen</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -11003,7 +11143,7 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>zurückgestellt (CON33-01)</t>
+          <t>Zeitcode vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="S120" t="inlineStr"/>
@@ -11044,12 +11184,22 @@
           <t>00:04:30:00</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>00:03:40:00</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>00:03:43:00</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>3</v>
+      </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>zurückgestellt, Kanon-Entscheidung CON33-01 offen</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -11080,7 +11230,7 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>zurückgestellt (CON33-01)</t>
+          <t>Zeitcode vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="S121" t="inlineStr"/>
@@ -14876,7 +15026,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>20-B (Shot-Bereich 01:00–02:15)</t>
+          <t>20-B (Shot-Bereich 01:00–02:15, Reprise 01:07:12–02:07:12)</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -14896,12 +15046,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>00:01:01:00</t>
+          <t>00:01:26:12</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>00:01:04:10</t>
+          <t>00:01:29:22</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -14909,7 +15059,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>vorläufig/geschätzt</t>
+          <t>vorläufig/geschätzt; folgt 1:1 aus C00 (+55,5 s)</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -14935,12 +15085,12 @@
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>81</t>
         </is>
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_001, Zeile 81)</t>
+          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_001, Zeile 81); Entscheidung 23.10.2026: volle 60 s, alle 8 Zeilen</t>
         </is>
       </c>
       <c r="S165" t="inlineStr"/>
@@ -14963,7 +15113,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>20-B (Shot-Bereich 01:00–02:15)</t>
+          <t>20-B (Shot-Bereich 01:00–02:15, Reprise 01:07:12–02:07:12)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -14983,12 +15133,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>00:01:05:00</t>
+          <t>00:01:30:12</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>00:01:08:22</t>
+          <t>00:01:34:10</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -14996,7 +15146,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>vorläufig/geschätzt</t>
+          <t>vorläufig/geschätzt; folgt 1:1 aus C00 (+55,5 s)</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -15019,15 +15169,19 @@
           <t>Ich weiß, dass du vieles anders machen wolltest.</t>
         </is>
       </c>
-      <c r="P166" t="inlineStr"/>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>sucht nicht nach einer beruhigenden Lüge</t>
+        </is>
+      </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>82</t>
         </is>
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_002, Zeile 82)</t>
+          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_002, Zeile 82); Entscheidung 23.10.2026: volle 60 s, alle 8 Zeilen</t>
         </is>
       </c>
       <c r="S166" t="inlineStr"/>
@@ -15050,7 +15204,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>20-B (Shot-Bereich 01:00–02:15)</t>
+          <t>20-B (Shot-Bereich 01:00–02:15, Reprise 01:07:12–02:07:12)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -15070,25 +15224,25 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>00:01:09:12</t>
+          <t>00:01:35:00</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>00:01:15:14</t>
+          <t>00:01:38:22</t>
         </is>
       </c>
       <c r="J167" t="n">
-        <v>6.1</v>
+        <v>3.9</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>vorläufig/geschätzt</t>
+          <t>vorläufig/geschätzt; folgt 1:1 aus C00 (+55,5 s)</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>TOCHTER</t>
+          <t>MANN, AUS C00 (ORIGINAL-O-TON)</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -15103,21 +15257,25 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Manche Dinge bleiben bei den Menschen. Auch wenn man es selbst nie erfährt.</t>
+          <t>Es gibt so viel, das ich nie …</t>
         </is>
       </c>
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>83</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_006, Zeile 86)</t>
-        </is>
-      </c>
-      <c r="S167" t="inlineStr"/>
+          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_003, Zeile 83); Entscheidung 23.10.2026: volle 60 s, alle 8 Zeilen</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>„so viel, das ich nie …“: nach „viel“ verlangt die Standardsprache „was“ (so viel, was …). Mögliche Absicht der Sprechweise – nicht geändert.</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -15137,45 +15295,45 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>20-C (Shot-Bereich 02:15–03:35)</t>
+          <t>20-B (Shot-Bereich 01:00–02:15, Reprise 01:07:12–02:07:12)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>20-C</t>
+          <t>20-B</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
+          <t>00:01:00:00</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
           <t>00:02:15:00</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>00:03:35:00</t>
-        </is>
-      </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>00:02:16:00</t>
+          <t>00:01:39:12</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>00:02:18:14</t>
+          <t>00:01:40:19</t>
         </is>
       </c>
       <c r="J168" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>vorläufig/geschätzt</t>
+          <t>vorläufig/geschätzt; folgt 1:1 aus C00 (+55,5 s)</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>TOCHTER, AUS C00 (ORIGINAL-O-TON)</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -15190,18 +15348,18 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Das … war mein Leben?</t>
+          <t>Ich weiß.</t>
         </is>
       </c>
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>84</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_004, Zeile 84); Entscheidung 23.10.2026: volle 60 s, alle 8 Zeilen</t>
         </is>
       </c>
       <c r="S168" t="inlineStr"/>
@@ -15224,45 +15382,45 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>20-C (Shot-Bereich 02:15–03:35)</t>
+          <t>20-B (Shot-Bereich 01:00–02:15, Reprise 01:07:12–02:07:12)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>20-C</t>
+          <t>20-B</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
+          <t>00:01:00:00</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
           <t>00:02:15:00</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>00:03:35:00</t>
-        </is>
-      </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>00:02:19:05</t>
+          <t>00:01:41:10</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>00:02:23:22</t>
+          <t>00:01:44:10</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>vorläufig/geschätzt</t>
+          <t>vorläufig/geschätzt; folgt 1:1 aus C00 (+55,5 s)</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>MANN, AUS C00 (ORIGINAL-O-TON)</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -15277,18 +15435,18 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Ein Leben vor den deinen. Dasselbe Echo. Nicht derselbe Mensch.</t>
+          <t>Und was, wenn nichts davon bleibt?</t>
         </is>
       </c>
       <c r="P169" t="inlineStr"/>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>85</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_005, Zeile 85); Entscheidung 23.10.2026: volle 60 s, alle 8 Zeilen</t>
         </is>
       </c>
       <c r="S169" t="inlineStr"/>
@@ -15311,45 +15469,45 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>20-C (Shot-Bereich 02:15–03:35)</t>
+          <t>20-B (Shot-Bereich 01:00–02:15, Reprise 01:07:12–02:07:12)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>20-C</t>
+          <t>20-B</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
+          <t>00:01:00:00</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
           <t>00:02:15:00</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>00:03:35:00</t>
-        </is>
-      </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>00:02:24:12</t>
+          <t>00:01:45:00</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>00:02:27:12</t>
+          <t>00:01:51:02</t>
         </is>
       </c>
       <c r="J170" t="n">
-        <v>3</v>
+        <v>6.1</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>vorläufig/geschätzt</t>
+          <t>vorläufig/geschätzt; folgt 1:1 aus C00 (+55,5 s)</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>TOCHTER, AUS C00 (ORIGINAL-O-TON)</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -15364,18 +15522,18 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Aber ich erinnere mich nicht daran.</t>
+          <t>Manche Dinge bleiben bei den Menschen. Auch wenn man es selbst nie erfährt.</t>
         </is>
       </c>
       <c r="P170" t="inlineStr"/>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>86</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_006, Zeile 86); Entscheidung 23.10.2026: volle 60 s, alle 8 Zeilen</t>
         </is>
       </c>
       <c r="S170" t="inlineStr"/>
@@ -15398,45 +15556,45 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>20-C (Shot-Bereich 02:15–03:35)</t>
+          <t>20-B (Shot-Bereich 01:00–02:15, Reprise 01:07:12–02:07:12)</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>20-C</t>
+          <t>20-B</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
+          <t>00:01:00:00</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
           <t>00:02:15:00</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>00:03:35:00</t>
-        </is>
-      </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>00:02:28:02</t>
+          <t>00:01:51:17</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>00:02:32:10</t>
+          <t>00:01:53:19</t>
         </is>
       </c>
       <c r="J171" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>vorläufig/geschätzt</t>
+          <t>vorläufig/geschätzt; folgt 1:1 aus C00 (+55,5 s)</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>MANN, AUS C00 (ORIGINAL-O-TON)</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -15451,18 +15609,18 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Weil ein neues Leben ein eigenes Leben sein muss.</t>
+          <t>Das weiß ich nicht.</t>
         </is>
       </c>
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>87</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_007, Zeile 87); Entscheidung 23.10.2026: volle 60 s, alle 8 Zeilen</t>
         </is>
       </c>
       <c r="S171" t="inlineStr"/>
@@ -15485,45 +15643,45 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>20-C (Shot-Bereich 02:15–03:35)</t>
+          <t>20-B (Shot-Bereich 01:00–02:15, Reprise 01:07:12–02:07:12)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>20-C</t>
+          <t>20-B</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
+          <t>00:01:00:00</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
           <t>00:02:15:00</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>00:03:35:00</t>
-        </is>
-      </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>00:02:33:00</t>
+          <t>00:01:54:10</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>00:02:34:17</t>
+          <t>00:01:58:17</t>
         </is>
       </c>
       <c r="J172" t="n">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>vorläufig/geschätzt</t>
+          <t>vorläufig/geschätzt; folgt 1:1 aus C00 (+55,5 s)</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>TOCHTER, AUS C00 (ORIGINAL-O-TON)</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -15538,18 +15696,18 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Und seine Tochter?</t>
+          <t>Du musst es jetzt nicht wissen. Ich bin hier.</t>
         </is>
       </c>
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>88</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_008, Zeile 88); Entscheidung 23.10.2026: volle 60 s, alle 8 Zeilen</t>
         </is>
       </c>
       <c r="S172" t="inlineStr"/>
@@ -15592,16 +15750,16 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>00:02:35:07</t>
+          <t>00:02:16:00</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>00:02:40:22</t>
+          <t>00:02:18:14</t>
         </is>
       </c>
       <c r="J173" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -15610,7 +15768,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>SPIELER-ECHO</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -15625,13 +15783,13 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Sie hatte ihr Leben. Ihre Geschichte ging weiter. Sie gehört nicht dir.</t>
+          <t>Das … war mein Leben?</t>
         </is>
       </c>
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>642</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
@@ -15659,36 +15817,36 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>20-D (Shot-Bereich 03:35–05:05)</t>
+          <t>20-C (Shot-Bereich 02:15–03:35)</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>20-D</t>
+          <t>20-C</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
+          <t>00:02:15:00</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
           <t>00:03:35:00</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>00:05:05:00</t>
-        </is>
-      </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>00:03:36:00</t>
+          <t>00:02:19:05</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>00:03:42:22</t>
+          <t>00:02:23:22</t>
         </is>
       </c>
       <c r="J174" t="n">
-        <v>6.9</v>
+        <v>4.7</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -15697,7 +15855,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>STIMMEN</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -15712,13 +15870,13 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Er wollte wissen, ob er genug getan hatte. Und ich stelle mir die gleiche Frage.</t>
+          <t>Ein Leben vor den deinen. Dasselbe Echo. Nicht derselbe Mensch.</t>
         </is>
       </c>
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>643</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
@@ -15726,11 +15884,7 @@
           <t>Zeitcode vorläufig/geschätzt</t>
         </is>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>„die gleiche Frage“ – gemeint ist dieselbe Frage; stilistisch, in Alltagssprache akzeptiert.</t>
-        </is>
-      </c>
+      <c r="S174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -15750,36 +15904,36 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>20-D (Shot-Bereich 03:35–05:05)</t>
+          <t>20-C (Shot-Bereich 02:15–03:35)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>20-D</t>
+          <t>20-C</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
+          <t>00:02:15:00</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
           <t>00:03:35:00</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>00:05:05:00</t>
-        </is>
-      </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>00:03:43:12</t>
+          <t>00:02:24:12</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>00:03:47:19</t>
+          <t>00:02:27:12</t>
         </is>
       </c>
       <c r="J175" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -15788,7 +15942,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>SPIELER-ECHO</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -15803,13 +15957,13 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Kein Leben lässt sich auf eine einzige Zahl reduzieren.</t>
+          <t>Aber ich erinnere mich nicht daran.</t>
         </is>
       </c>
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>644</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
@@ -15837,36 +15991,36 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>20-D (Shot-Bereich 03:35–05:05)</t>
+          <t>20-C (Shot-Bereich 02:15–03:35)</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>20-D</t>
+          <t>20-C</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
+          <t>00:02:15:00</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
           <t>00:03:35:00</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>00:05:05:00</t>
-        </is>
-      </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>00:03:48:10</t>
+          <t>00:02:28:02</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>00:03:51:00</t>
+          <t>00:02:32:10</t>
         </is>
       </c>
       <c r="J176" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -15875,7 +16029,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>STIMMEN</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -15890,13 +16044,13 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Aber ich habe andere verändert.</t>
+          <t>Weil ein neues Leben ein eigenes Leben sein muss.</t>
         </is>
       </c>
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>645</t>
         </is>
       </c>
       <c r="R176" t="inlineStr">
@@ -15924,36 +16078,36 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>20-D (Shot-Bereich 03:35–05:05)</t>
+          <t>20-C (Shot-Bereich 02:15–03:35)</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>20-D</t>
+          <t>20-C</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
+          <t>00:02:15:00</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
           <t>00:03:35:00</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>00:05:05:00</t>
-        </is>
-      </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>00:03:51:14</t>
+          <t>00:02:33:00</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>00:03:54:05</t>
+          <t>00:02:34:17</t>
         </is>
       </c>
       <c r="J177" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
@@ -15962,7 +16116,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>SPIELER-ECHO</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -15977,13 +16131,13 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Und sie haben dich verändert.</t>
+          <t>Und seine Tochter?</t>
         </is>
       </c>
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>646</t>
         </is>
       </c>
       <c r="R177" t="inlineStr">
@@ -16011,36 +16165,36 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>20-D (Shot-Bereich 03:35–05:05)</t>
+          <t>20-C (Shot-Bereich 02:15–03:35)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>20-D</t>
+          <t>20-C</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
+          <t>00:02:15:00</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
           <t>00:03:35:00</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>00:05:05:00</t>
-        </is>
-      </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>00:03:54:19</t>
+          <t>00:02:35:07</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>00:03:59:02</t>
+          <t>00:02:40:22</t>
         </is>
       </c>
       <c r="J178" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -16049,7 +16203,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>STIMMEN</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -16064,13 +16218,13 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>Dann gibt es keinen Weg, alles richtig zu machen?</t>
+          <t>Sie hatte ihr Leben. Ihre Geschichte ging weiter. Sie gehört nicht dir.</t>
         </is>
       </c>
       <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>647</t>
         </is>
       </c>
       <c r="R178" t="inlineStr">
@@ -16118,16 +16272,16 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>00:03:59:17</t>
+          <t>00:03:36:00</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>00:04:02:17</t>
+          <t>00:03:42:22</t>
         </is>
       </c>
       <c r="J179" t="n">
-        <v>3</v>
+        <v>6.9</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -16136,7 +16290,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>SPIELER-ECHO</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -16151,13 +16305,13 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>Es gibt Verantwortung. Keine vollständige Kontrolle.</t>
+          <t>Er wollte wissen, ob er genug getan hatte. Und ich stelle mir die gleiche Frage.</t>
         </is>
       </c>
       <c r="P179" t="inlineStr"/>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>651</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
@@ -16165,7 +16319,11 @@
           <t>Zeitcode vorläufig/geschätzt</t>
         </is>
       </c>
-      <c r="S179" t="inlineStr"/>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>„die gleiche Frage“ – gemeint ist dieselbe Frage; stilistisch, in Alltagssprache akzeptiert.</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -16185,36 +16343,36 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>20-E (Shot-Bereich 05:05–06:32)</t>
+          <t>20-D (Shot-Bereich 03:35–05:05)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>20-E</t>
+          <t>20-D</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
+          <t>00:03:35:00</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
           <t>00:05:05:00</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>00:06:32:00</t>
-        </is>
-      </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>00:05:06:00</t>
+          <t>00:03:43:12</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>00:05:09:00</t>
+          <t>00:03:47:19</t>
         </is>
       </c>
       <c r="J180" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -16223,7 +16381,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>STIMMEN</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -16238,13 +16396,13 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>Wer hat dann diese Welt erschaffen?</t>
+          <t>Kein Leben lässt sich auf eine einzige Zahl reduzieren.</t>
         </is>
       </c>
       <c r="P180" t="inlineStr"/>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>652</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
@@ -16272,36 +16430,36 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>20-E (Shot-Bereich 05:05–06:32)</t>
+          <t>20-D (Shot-Bereich 03:35–05:05)</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>20-E</t>
+          <t>20-D</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
+          <t>00:03:35:00</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
           <t>00:05:05:00</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>00:06:32:00</t>
-        </is>
-      </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>00:05:09:14</t>
+          <t>00:03:48:10</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>00:05:12:14</t>
+          <t>00:03:51:00</t>
         </is>
       </c>
       <c r="J181" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -16310,7 +16468,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>SPIELER-ECHO</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -16325,13 +16483,13 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>Den ersten Ursprung kennen wir nicht.</t>
+          <t>Aber ich habe andere verändert.</t>
         </is>
       </c>
       <c r="P181" t="inlineStr"/>
       <c r="Q181" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>653</t>
         </is>
       </c>
       <c r="R181" t="inlineStr">
@@ -16359,36 +16517,36 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>20-E (Shot-Bereich 05:05–06:32)</t>
+          <t>20-D (Shot-Bereich 03:35–05:05)</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>20-E</t>
+          <t>20-D</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
+          <t>00:03:35:00</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
           <t>00:05:05:00</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>00:06:32:00</t>
-        </is>
-      </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>00:05:14:17</t>
+          <t>00:03:51:14</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>00:05:24:05</t>
+          <t>00:03:54:05</t>
         </is>
       </c>
       <c r="J182" t="n">
-        <v>9.5</v>
+        <v>2.6</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -16412,13 +16570,13 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>Aber die Welt, in der Menschen leben – ihre Häuser, Geschichten, Hoffnungen, ihre Wunden und ihre Möglichkeiten – formen sie miteinander.</t>
+          <t>Und sie haben dich verändert.</t>
         </is>
       </c>
       <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>654</t>
         </is>
       </c>
       <c r="R182" t="inlineStr">
@@ -16446,36 +16604,36 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>20-E (Shot-Bereich 05:05–06:32)</t>
+          <t>20-D (Shot-Bereich 03:35–05:05)</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>20-E</t>
+          <t>20-D</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
+          <t>00:03:35:00</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
           <t>00:05:05:00</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>00:06:32:00</t>
-        </is>
-      </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>00:05:24:19</t>
+          <t>00:03:54:19</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>00:05:26:02</t>
+          <t>00:03:59:02</t>
         </is>
       </c>
       <c r="J183" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -16499,13 +16657,13 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>Wir alle?</t>
+          <t>Dann gibt es keinen Weg, alles richtig zu machen?</t>
         </is>
       </c>
       <c r="P183" t="inlineStr"/>
       <c r="Q183" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>655</t>
         </is>
       </c>
       <c r="R183" t="inlineStr">
@@ -16533,36 +16691,36 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>20-E (Shot-Bereich 05:05–06:32)</t>
+          <t>20-D (Shot-Bereich 03:35–05:05)</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>20-E</t>
+          <t>20-D</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
+          <t>00:03:35:00</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
           <t>00:05:05:00</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>00:06:32:00</t>
-        </is>
-      </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>00:05:26:17</t>
+          <t>00:03:59:17</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>00:05:33:14</t>
+          <t>00:04:02:17</t>
         </is>
       </c>
       <c r="J184" t="n">
-        <v>6.9</v>
+        <v>3</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -16586,13 +16744,13 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>Mit jedem Leben. Mit dem, was wir tun. Und mit dem, was wir anderen ermöglichen.</t>
+          <t>Es gibt Verantwortung. Keine vollständige Kontrolle.</t>
         </is>
       </c>
       <c r="P184" t="inlineStr"/>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>656</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
@@ -16620,36 +16778,36 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>20-F (Shot-Bereich 06:32–07:40)</t>
+          <t>20-E (Shot-Bereich 05:05–06:32)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>20-F</t>
+          <t>20-E</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
+          <t>00:05:05:00</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
           <t>00:06:32:00</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>00:07:40:00</t>
-        </is>
-      </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>00:06:33:00</t>
+          <t>00:05:06:00</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>00:06:35:02</t>
+          <t>00:05:09:00</t>
         </is>
       </c>
       <c r="J185" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -16673,13 +16831,13 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>Sind wir die Schöpfer?</t>
+          <t>Wer hat dann diese Welt erschaffen?</t>
         </is>
       </c>
       <c r="P185" t="inlineStr"/>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>660</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
@@ -16707,36 +16865,36 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>20-F (Shot-Bereich 06:32–07:40)</t>
+          <t>20-E (Shot-Bereich 05:05–06:32)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>20-F</t>
+          <t>20-E</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
+          <t>00:05:05:00</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
           <t>00:06:32:00</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>00:07:40:00</t>
-        </is>
-      </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>00:06:35:17</t>
+          <t>00:05:09:14</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>00:06:40:22</t>
+          <t>00:05:12:14</t>
         </is>
       </c>
       <c r="J186" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -16760,13 +16918,13 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Wir sind Mitgestalter. Keiner von uns besitzt das Leben eines anderen.</t>
+          <t>Den ersten Ursprung kennen wir nicht.</t>
         </is>
       </c>
       <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>661</t>
         </is>
       </c>
       <c r="R186" t="inlineStr">
@@ -16794,36 +16952,36 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>20-F (Shot-Bereich 06:32–07:40)</t>
+          <t>20-E (Shot-Bereich 05:05–06:32)</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>20-F</t>
+          <t>20-E</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
+          <t>00:05:05:00</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
           <t>00:06:32:00</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>00:07:40:00</t>
-        </is>
-      </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>00:06:41:12</t>
+          <t>00:05:14:17</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>00:06:43:05</t>
+          <t>00:05:24:05</t>
         </is>
       </c>
       <c r="J187" t="n">
-        <v>1.7</v>
+        <v>9.5</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
@@ -16832,7 +16990,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>STIMMEN</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -16847,13 +17005,13 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>Und das hier?</t>
+          <t>Aber die Welt, in der Menschen leben – ihre Häuser, Geschichten, Hoffnungen, ihre Wunden und ihre Möglichkeiten – formen sie miteinander.</t>
         </is>
       </c>
       <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>663</t>
         </is>
       </c>
       <c r="R187" t="inlineStr">
@@ -16881,36 +17039,36 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>20-F (Shot-Bereich 06:32–07:40)</t>
+          <t>20-E (Shot-Bereich 05:05–06:32)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>20-F</t>
+          <t>20-E</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
+          <t>00:05:05:00</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
           <t>00:06:32:00</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>00:07:40:00</t>
-        </is>
-      </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>00:06:43:19</t>
+          <t>00:05:24:19</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>00:06:51:14</t>
+          <t>00:05:26:02</t>
         </is>
       </c>
       <c r="J188" t="n">
-        <v>7.8</v>
+        <v>1.3</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -16919,7 +17077,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>SPIELER-ECHO</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -16934,13 +17092,13 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>Eine Möglichkeit, Bedingungen für eine neue Welt zu schaffen. Das Leben darin wird seinen eigenen Weg finden.</t>
+          <t>Wir alle?</t>
         </is>
       </c>
       <c r="P188" t="inlineStr"/>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>664</t>
         </is>
       </c>
       <c r="R188" t="inlineStr">
@@ -16968,36 +17126,36 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20-G (Shot-Bereich 07:40–09:00)</t>
+          <t>20-E (Shot-Bereich 05:05–06:32)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>20-G</t>
+          <t>20-E</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>00:07:40:00</t>
+          <t>00:05:05:00</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>00:09:00:00</t>
+          <t>00:06:32:00</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>00:07:41:00</t>
+          <t>00:05:26:17</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>00:07:46:05</t>
+          <t>00:05:33:14</t>
         </is>
       </c>
       <c r="J189" t="n">
-        <v>5.2</v>
+        <v>6.9</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -17006,7 +17164,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>STIMMEN</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -17021,13 +17179,13 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>Wenn ich mich entscheide … weiß ich dann, was daraus wird?</t>
+          <t>Mit jedem Leben. Mit dem, was wir tun. Und mit dem, was wir anderen ermöglichen.</t>
         </is>
       </c>
       <c r="P189" t="inlineStr"/>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>665</t>
         </is>
       </c>
       <c r="R189" t="inlineStr">
@@ -17055,36 +17213,36 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>20-G (Shot-Bereich 07:40–09:00)</t>
+          <t>20-F (Shot-Bereich 06:32–07:40)</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>20-G</t>
+          <t>20-F</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
+          <t>00:06:32:00</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
           <t>00:07:40:00</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>00:09:00:00</t>
-        </is>
-      </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>00:07:46:19</t>
+          <t>00:06:33:00</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>00:07:47:14</t>
+          <t>00:06:35:02</t>
         </is>
       </c>
       <c r="J190" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -17093,7 +17251,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>SPIELER-ECHO</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -17108,13 +17266,13 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Nein.</t>
+          <t>Sind wir die Schöpfer?</t>
         </is>
       </c>
       <c r="P190" t="inlineStr"/>
       <c r="Q190" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>669</t>
         </is>
       </c>
       <c r="R190" t="inlineStr">
@@ -17142,36 +17300,36 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>20-G (Shot-Bereich 07:40–09:00)</t>
+          <t>20-F (Shot-Bereich 06:32–07:40)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>20-G</t>
+          <t>20-F</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
+          <t>00:06:32:00</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
           <t>00:07:40:00</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>00:09:00:00</t>
-        </is>
-      </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>00:07:48:05</t>
+          <t>00:06:35:17</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>00:07:50:19</t>
+          <t>00:06:40:22</t>
         </is>
       </c>
       <c r="J191" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -17180,7 +17338,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>STIMMEN</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -17195,13 +17353,13 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>Dann kann ich Fehler machen.</t>
+          <t>Wir sind Mitgestalter. Keiner von uns besitzt das Leben eines anderen.</t>
         </is>
       </c>
       <c r="P191" t="inlineStr"/>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>670</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
@@ -17229,36 +17387,36 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>20-G (Shot-Bereich 07:40–09:00)</t>
+          <t>20-F (Shot-Bereich 06:32–07:40)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>20-G</t>
+          <t>20-F</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
+          <t>00:06:32:00</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
           <t>00:07:40:00</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>00:09:00:00</t>
-        </is>
-      </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>00:07:51:10</t>
+          <t>00:06:41:12</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>00:07:52:05</t>
+          <t>00:06:43:05</t>
         </is>
       </c>
       <c r="J192" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -17267,7 +17425,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>SPIELER-ECHO</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -17282,13 +17440,13 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>Ja.</t>
+          <t>Und das hier?</t>
         </is>
       </c>
       <c r="P192" t="inlineStr"/>
       <c r="Q192" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>671</t>
         </is>
       </c>
       <c r="R192" t="inlineStr">
@@ -17316,36 +17474,36 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>20-G (Shot-Bereich 07:40–09:00)</t>
+          <t>20-F (Shot-Bereich 06:32–07:40)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>20-G</t>
+          <t>20-F</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
+          <t>00:06:32:00</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
           <t>00:07:40:00</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>00:09:00:00</t>
-        </is>
-      </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>00:07:52:19</t>
+          <t>00:06:43:19</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>00:07:55:10</t>
+          <t>00:06:51:14</t>
         </is>
       </c>
       <c r="J193" t="n">
-        <v>2.6</v>
+        <v>7.8</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -17354,7 +17512,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>STIMMEN</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -17369,13 +17527,13 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>Und trotzdem darf ich anfangen?</t>
+          <t>Eine Möglichkeit, Bedingungen für eine neue Welt zu schaffen. Das Leben darin wird seinen eigenen Weg finden.</t>
         </is>
       </c>
       <c r="P193" t="inlineStr"/>
       <c r="Q193" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>672</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
@@ -17423,16 +17581,16 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>00:07:56:00</t>
+          <t>00:07:41:00</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>00:07:58:14</t>
+          <t>00:07:46:05</t>
         </is>
       </c>
       <c r="J194" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -17441,7 +17599,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>SPIELER-ECHO</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -17456,13 +17614,13 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>Du darfst mitgestalten. Nicht herrschen.</t>
+          <t>Wenn ich mich entscheide … weiß ich dann, was daraus wird?</t>
         </is>
       </c>
       <c r="P194" t="inlineStr"/>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>676</t>
         </is>
       </c>
       <c r="R194" t="inlineStr">
@@ -17475,51 +17633,51 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>VO_C21_001</t>
+          <t>VO_C20_034</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SUB_C21_001</t>
+          <t>SUB_C20_034</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>C21</t>
+          <t>C20</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>21-D (Shot-Bereich 02:25–03:10)</t>
+          <t>20-G (Shot-Bereich 07:40–09:00)</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>21-D</t>
+          <t>20-G</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>00:02:25:00</t>
+          <t>00:07:40:00</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>00:03:10:00</t>
+          <t>00:09:00:00</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>00:02:26:00</t>
+          <t>00:07:46:19</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>00:02:29:22</t>
+          <t>00:07:47:14</t>
         </is>
       </c>
       <c r="J195" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
@@ -17543,17 +17701,13 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Wir wissen nicht, wer sie einmal sein werden.</t>
-        </is>
-      </c>
-      <c r="P195" t="inlineStr">
-        <is>
-          <t>fast unhörbar, nicht als verkündender Erzähler</t>
-        </is>
-      </c>
+          <t>Nein.</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr"/>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>677</t>
         </is>
       </c>
       <c r="R195" t="inlineStr">
@@ -17566,51 +17720,51 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>VO_C21_002</t>
+          <t>VO_C20_035</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SUB_C21_002</t>
+          <t>SUB_C20_035</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>C21</t>
+          <t>C20</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>21-D (Shot-Bereich 02:25–03:10)</t>
+          <t>20-G (Shot-Bereich 07:40–09:00)</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>21-D</t>
+          <t>20-G</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>00:02:25:00</t>
+          <t>00:07:40:00</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>00:03:10:00</t>
+          <t>00:09:00:00</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>00:02:32:00</t>
+          <t>00:07:48:05</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>00:02:34:02</t>
+          <t>00:07:50:19</t>
         </is>
       </c>
       <c r="J196" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
@@ -17619,7 +17773,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>SPIELER-ECHO</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -17634,24 +17788,463 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>Das ist ihr Leben.</t>
+          <t>Dann kann ich Fehler machen.</t>
         </is>
       </c>
       <c r="P196" t="inlineStr"/>
       <c r="Q196" t="inlineStr">
         <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>Zeitcode vorläufig/geschätzt</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>VO_C20_036</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>SUB_C20_036</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>C20</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>20-G (Shot-Bereich 07:40–09:00)</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>20-G</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>00:07:40:00</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>00:09:00:00</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>00:07:51:10</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>00:07:52:05</t>
+        </is>
+      </c>
+      <c r="J197" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>vorläufig/geschätzt</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>STIMMEN</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>de-DE</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Ja.</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>Zeitcode vorläufig/geschätzt</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>VO_C20_037</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>SUB_C20_037</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>C20</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>20-G (Shot-Bereich 07:40–09:00)</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>20-G</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>00:07:40:00</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>00:09:00:00</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>00:07:52:19</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>00:07:55:10</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>vorläufig/geschätzt</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>SPIELER-ECHO</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>de-DE</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Und trotzdem darf ich anfangen?</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>Zeitcode vorläufig/geschätzt</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>VO_C20_038</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>SUB_C20_038</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>C20</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>20-G (Shot-Bereich 07:40–09:00)</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>20-G</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>00:07:40:00</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>00:09:00:00</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>00:07:56:00</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>00:07:58:14</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>vorläufig/geschätzt</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>STIMMEN</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>de-DE</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Du darfst mitgestalten. Nicht herrschen.</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>Zeitcode vorläufig/geschätzt</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>VO_C21_001</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>SUB_C21_001</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>C21</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>21-D (Shot-Bereich 02:25–03:10)</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>21-D</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>00:02:25:00</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>00:03:10:00</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>00:02:26:00</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>00:02:29:22</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>vorläufig/geschätzt</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>STIMMEN</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>de-DE</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Wir wissen nicht, wer sie einmal sein werden.</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>fast unhörbar, nicht als verkündender Erzähler</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>Zeitcode vorläufig/geschätzt</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>VO_C21_002</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>SUB_C21_002</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>C21</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>21-D (Shot-Bereich 02:25–03:10)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>21-D</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>00:02:25:00</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>00:03:10:00</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>00:02:32:00</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>00:02:34:02</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>vorläufig/geschätzt</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>STIMMEN</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>de-DE</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Das ist ihr Leben.</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr">
+        <is>
           <t>701</t>
         </is>
       </c>
-      <c r="R196" t="inlineStr">
+      <c r="R201" t="inlineStr">
         <is>
           <t>Zeitcode vorläufig/geschätzt</t>
         </is>
       </c>
-      <c r="S196" t="inlineStr"/>
+      <c r="S201" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S196"/>
+  <autoFilter ref="A1:S201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/audio_cinematics/genesis_sprachzeilen_C00-C21.xlsx
+++ b/docs/audio_cinematics/genesis_sprachzeilen_C00-C21.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprachzeilen" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet'!$A$1:$S$201</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -561,8 +559,10 @@
           <t>00:00:34:10</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>3.4</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt; Reprise C20, Originalton</t>
+          <t>Zeitcode vorläufig/geschätzt; einmal erzeugen, einfrieren, SHA256, nie neu erzeugen</t>
         </is>
       </c>
       <c r="S2" t="inlineStr"/>
@@ -648,8 +648,10 @@
           <t>00:00:38:22</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>3.9</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -688,7 +690,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt; Reprise C20, Originalton</t>
+          <t>Zeitcode vorläufig/geschätzt; einmal erzeugen, einfrieren, SHA256, nie neu erzeugen</t>
         </is>
       </c>
       <c r="S3" t="inlineStr"/>
@@ -739,8 +741,10 @@
           <t>00:00:43:10</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>3.9</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -830,8 +834,10 @@
           <t>00:00:45:07</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>1.3</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -917,8 +923,10 @@
           <t>00:00:48:22</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>3</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1004,8 +1012,10 @@
           <t>00:00:55:14</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>6.1</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1040,7 +1050,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt; Reprise C20, Originalton</t>
+          <t>Zeitcode vorläufig/geschätzt; einmal erzeugen, einfrieren, SHA256, nie neu erzeugen</t>
         </is>
       </c>
       <c r="S7" t="inlineStr"/>
@@ -1091,8 +1101,10 @@
           <t>00:00:58:07</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>2.1</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1178,8 +1190,10 @@
           <t>00:01:03:05</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>4.3</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1265,8 +1279,10 @@
           <t>00:00:21:22</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>3.9</v>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1356,8 +1372,10 @@
           <t>00:00:27:10</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>3.4</v>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1443,8 +1461,10 @@
           <t>00:00:31:02</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>2.1</v>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1534,8 +1554,10 @@
           <t>00:00:37:22</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>4.7</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1621,8 +1643,10 @@
           <t>00:00:42:02</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>2.1</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1708,8 +1732,10 @@
           <t>00:00:04:10</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>3.4</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1799,8 +1825,10 @@
           <t>00:00:06:07</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>1.3</v>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1894,8 +1922,10 @@
           <t>00:01:05:17</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>1.7</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1985,8 +2015,10 @@
           <t>00:01:08:00</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>1.7</v>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2076,8 +2108,10 @@
           <t>00:00:23:02</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>2.1</v>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2167,8 +2201,10 @@
           <t>00:00:39:17</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v>1.7</v>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2258,8 +2294,10 @@
           <t>00:00:33:12</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>6.5</v>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2349,8 +2387,10 @@
           <t>00:00:36:17</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>2.6</v>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2440,8 +2480,10 @@
           <t>00:00:50:02</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>2.1</v>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2527,8 +2569,10 @@
           <t>00:01:15:02</t>
         </is>
       </c>
-      <c r="J24" t="n">
-        <v>2.1</v>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2622,8 +2666,10 @@
           <t>00:01:15:14</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>2.6</v>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2717,8 +2763,10 @@
           <t>00:01:16:10</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>3.4</v>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2812,8 +2860,10 @@
           <t>00:01:44:00</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>3</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2903,8 +2953,10 @@
           <t>00:01:44:10</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>3.4</v>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2994,8 +3046,10 @@
           <t>00:01:44:00</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>3</v>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -3085,8 +3139,10 @@
           <t>00:00:31:05</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>5.2</v>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -3172,8 +3228,10 @@
           <t>00:00:35:17</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>3.9</v>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -3259,8 +3317,10 @@
           <t>00:00:41:05</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>3.4</v>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -3350,8 +3410,10 @@
           <t>00:01:01:22</t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v>3.9</v>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -3437,8 +3499,10 @@
           <t>00:01:05:02</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>2.6</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3524,8 +3588,10 @@
           <t>00:01:09:02</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>3.4</v>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3611,8 +3677,10 @@
           <t>00:01:29:07</t>
         </is>
       </c>
-      <c r="J36" t="n">
-        <v>4.3</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3698,8 +3766,10 @@
           <t>00:01:31:14</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>1.7</v>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3789,8 +3859,10 @@
           <t>00:01:32:12</t>
         </is>
       </c>
-      <c r="J38" t="n">
-        <v>2.6</v>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3880,8 +3952,10 @@
           <t>00:01:33:07</t>
         </is>
       </c>
-      <c r="J39" t="n">
-        <v>3.4</v>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3971,8 +4045,10 @@
           <t>00:00:05:17</t>
         </is>
       </c>
-      <c r="J40" t="n">
-        <v>4.7</v>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -4058,8 +4134,10 @@
           <t>00:00:07:02</t>
         </is>
       </c>
-      <c r="J41" t="n">
-        <v>0.8</v>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -4149,8 +4227,10 @@
           <t>00:00:08:00</t>
         </is>
       </c>
-      <c r="J42" t="n">
-        <v>1.7</v>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -4240,8 +4320,10 @@
           <t>00:00:33:17</t>
         </is>
       </c>
-      <c r="J43" t="n">
-        <v>4.7</v>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -4327,8 +4409,10 @@
           <t>00:00:41:22</t>
         </is>
       </c>
-      <c r="J44" t="n">
-        <v>6.1</v>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -4414,8 +4498,10 @@
           <t>00:00:45:02</t>
         </is>
       </c>
-      <c r="J45" t="n">
-        <v>2.6</v>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4505,8 +4591,10 @@
           <t>00:00:49:14</t>
         </is>
       </c>
-      <c r="J46" t="n">
-        <v>3.9</v>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4596,8 +4684,10 @@
           <t>00:01:09:12</t>
         </is>
       </c>
-      <c r="J47" t="n">
-        <v>6.5</v>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4683,8 +4773,10 @@
           <t>00:01:13:17</t>
         </is>
       </c>
-      <c r="J48" t="n">
-        <v>2.1</v>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -4770,8 +4862,10 @@
           <t>00:01:38:22</t>
         </is>
       </c>
-      <c r="J49" t="n">
-        <v>3.9</v>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4861,8 +4955,10 @@
           <t>00:01:38:10</t>
         </is>
       </c>
-      <c r="J50" t="n">
-        <v>3.4</v>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4952,8 +5048,10 @@
           <t>00:01:37:14</t>
         </is>
       </c>
-      <c r="J51" t="n">
-        <v>2.6</v>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -5043,8 +5141,10 @@
           <t>00:01:38:00</t>
         </is>
       </c>
-      <c r="J52" t="n">
-        <v>3</v>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -5134,8 +5234,10 @@
           <t>00:01:36:17</t>
         </is>
       </c>
-      <c r="J53" t="n">
-        <v>1.7</v>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -5225,8 +5327,10 @@
           <t>00:01:42:02</t>
         </is>
       </c>
-      <c r="J54" t="n">
-        <v>2.6</v>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -5316,8 +5420,10 @@
           <t>00:01:48:07</t>
         </is>
       </c>
-      <c r="J55" t="n">
-        <v>5.6</v>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -5403,8 +5509,10 @@
           <t>00:01:52:19</t>
         </is>
       </c>
-      <c r="J56" t="n">
-        <v>3.9</v>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -5490,8 +5598,10 @@
           <t>00:01:57:07</t>
         </is>
       </c>
-      <c r="J57" t="n">
-        <v>3.9</v>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -5581,8 +5691,10 @@
           <t>00:02:01:07</t>
         </is>
       </c>
-      <c r="J58" t="n">
-        <v>3.4</v>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5672,8 +5784,10 @@
           <t>00:02:06:14</t>
         </is>
       </c>
-      <c r="J59" t="n">
-        <v>4.7</v>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5759,8 +5873,10 @@
           <t>00:00:31:02</t>
         </is>
       </c>
-      <c r="J60" t="n">
-        <v>2.1</v>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5846,8 +5962,10 @@
           <t>00:00:33:10</t>
         </is>
       </c>
-      <c r="J61" t="n">
-        <v>1.7</v>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5933,8 +6051,10 @@
           <t>00:00:33:19</t>
         </is>
       </c>
-      <c r="J62" t="n">
-        <v>2.1</v>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -6020,8 +6140,10 @@
           <t>00:00:53:00</t>
         </is>
       </c>
-      <c r="J63" t="n">
-        <v>3</v>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -6107,8 +6229,10 @@
           <t>00:00:54:22</t>
         </is>
       </c>
-      <c r="J64" t="n">
-        <v>1.3</v>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -6198,8 +6322,10 @@
           <t>00:00:58:02</t>
         </is>
       </c>
-      <c r="J65" t="n">
-        <v>2.6</v>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -6289,8 +6415,10 @@
           <t>00:00:27:14</t>
         </is>
       </c>
-      <c r="J66" t="n">
-        <v>2.6</v>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -6376,8 +6504,10 @@
           <t>00:00:29:00</t>
         </is>
       </c>
-      <c r="J67" t="n">
-        <v>0.8</v>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -6467,8 +6597,10 @@
           <t>00:00:33:00</t>
         </is>
       </c>
-      <c r="J68" t="n">
-        <v>3.4</v>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6554,8 +6686,10 @@
           <t>00:01:00:19</t>
         </is>
       </c>
-      <c r="J69" t="n">
-        <v>7.8</v>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6641,8 +6775,10 @@
           <t>00:01:10:12</t>
         </is>
       </c>
-      <c r="J70" t="n">
-        <v>9.1</v>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6732,8 +6868,10 @@
           <t>00:01:18:00</t>
         </is>
       </c>
-      <c r="J71" t="n">
-        <v>6.9</v>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6819,8 +6957,10 @@
           <t>00:01:36:00</t>
         </is>
       </c>
-      <c r="J72" t="n">
-        <v>3</v>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6910,8 +7050,10 @@
           <t>00:01:34:17</t>
         </is>
       </c>
-      <c r="J73" t="n">
-        <v>1.7</v>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -7001,8 +7143,10 @@
           <t>00:01:35:02</t>
         </is>
       </c>
-      <c r="J74" t="n">
-        <v>2.1</v>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -7092,8 +7236,10 @@
           <t>00:01:36:00</t>
         </is>
       </c>
-      <c r="J75" t="n">
-        <v>3</v>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -7183,8 +7329,10 @@
           <t>00:01:33:19</t>
         </is>
       </c>
-      <c r="J76" t="n">
-        <v>0.8</v>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -7274,8 +7422,10 @@
           <t>00:01:41:07</t>
         </is>
       </c>
-      <c r="J77" t="n">
-        <v>4.7</v>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -7365,8 +7515,10 @@
           <t>00:01:44:22</t>
         </is>
       </c>
-      <c r="J78" t="n">
-        <v>3</v>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -7456,8 +7608,10 @@
           <t>00:01:48:22</t>
         </is>
       </c>
-      <c r="J79" t="n">
-        <v>3.4</v>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -7547,8 +7701,10 @@
           <t>00:00:07:02</t>
         </is>
       </c>
-      <c r="J80" t="n">
-        <v>6.1</v>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -7638,8 +7794,10 @@
           <t>00:00:38:10</t>
         </is>
       </c>
-      <c r="J81" t="n">
-        <v>7.4</v>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -7725,8 +7883,10 @@
           <t>00:00:40:17</t>
         </is>
       </c>
-      <c r="J82" t="n">
-        <v>1.7</v>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -7816,8 +7976,10 @@
           <t>00:00:41:02</t>
         </is>
       </c>
-      <c r="J83" t="n">
-        <v>2.1</v>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7907,8 +8069,10 @@
           <t>00:00:40:17</t>
         </is>
       </c>
-      <c r="J84" t="n">
-        <v>1.7</v>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7998,8 +8162,10 @@
           <t>00:01:06:17</t>
         </is>
       </c>
-      <c r="J85" t="n">
-        <v>8.699999999999999</v>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -8085,8 +8251,10 @@
           <t>00:01:09:10</t>
         </is>
       </c>
-      <c r="J86" t="n">
-        <v>2.1</v>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -8176,8 +8344,10 @@
           <t>00:01:36:02</t>
         </is>
       </c>
-      <c r="J87" t="n">
-        <v>2.1</v>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -8263,8 +8433,10 @@
           <t>00:01:40:02</t>
         </is>
       </c>
-      <c r="J88" t="n">
-        <v>3.4</v>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -8358,8 +8530,10 @@
           <t>00:01:45:00</t>
         </is>
       </c>
-      <c r="J89" t="n">
-        <v>4.3</v>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -8449,8 +8623,10 @@
           <t>00:01:47:17</t>
         </is>
       </c>
-      <c r="J90" t="n">
-        <v>2.1</v>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -8540,8 +8716,10 @@
           <t>00:00:28:02</t>
         </is>
       </c>
-      <c r="J91" t="n">
-        <v>2.1</v>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -8631,8 +8809,10 @@
           <t>00:00:30:10</t>
         </is>
       </c>
-      <c r="J92" t="n">
-        <v>1.7</v>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -8722,8 +8902,10 @@
           <t>00:00:03:02</t>
         </is>
       </c>
-      <c r="J93" t="n">
-        <v>2.1</v>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -8813,8 +8995,10 @@
           <t>00:01:11:02</t>
         </is>
       </c>
-      <c r="J94" t="n">
-        <v>2.1</v>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -8900,8 +9084,10 @@
           <t>00:01:12:12</t>
         </is>
       </c>
-      <c r="J95" t="n">
-        <v>0.8</v>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -8987,8 +9173,10 @@
           <t>00:01:16:02</t>
         </is>
       </c>
-      <c r="J96" t="n">
-        <v>3</v>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -9074,8 +9262,10 @@
           <t>00:01:21:14</t>
         </is>
       </c>
-      <c r="J97" t="n">
-        <v>3.4</v>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -9161,8 +9351,10 @@
           <t>00:01:45:02</t>
         </is>
       </c>
-      <c r="J98" t="n">
-        <v>2.1</v>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -9252,8 +9444,10 @@
           <t>00:01:47:19</t>
         </is>
       </c>
-      <c r="J99" t="n">
-        <v>2.1</v>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -9343,8 +9537,10 @@
           <t>00:01:49:17</t>
         </is>
       </c>
-      <c r="J100" t="n">
-        <v>1.3</v>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -9430,8 +9626,10 @@
           <t>00:01:55:00</t>
         </is>
       </c>
-      <c r="J101" t="n">
-        <v>4.7</v>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -9517,8 +9715,10 @@
           <t>00:00:32:17</t>
         </is>
       </c>
-      <c r="J102" t="n">
-        <v>1.7</v>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -9604,8 +9804,10 @@
           <t>00:00:36:07</t>
         </is>
       </c>
-      <c r="J103" t="n">
-        <v>3</v>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -9699,8 +9901,10 @@
           <t>00:00:39:12</t>
         </is>
       </c>
-      <c r="J104" t="n">
-        <v>2.6</v>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -9786,8 +9990,10 @@
           <t>00:00:42:17</t>
         </is>
       </c>
-      <c r="J105" t="n">
-        <v>2.6</v>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -9873,8 +10079,10 @@
           <t>00:00:44:14</t>
         </is>
       </c>
-      <c r="J106" t="n">
-        <v>1.3</v>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -9960,8 +10168,10 @@
           <t>00:01:05:17</t>
         </is>
       </c>
-      <c r="J107" t="n">
-        <v>1.7</v>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -10051,8 +10261,10 @@
           <t>00:01:34:00</t>
         </is>
       </c>
-      <c r="J108" t="n">
-        <v>3</v>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -10142,8 +10354,10 @@
           <t>00:01:40:00</t>
         </is>
       </c>
-      <c r="J109" t="n">
-        <v>3.9</v>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -10229,8 +10443,10 @@
           <t>00:00:04:00</t>
         </is>
       </c>
-      <c r="J110" t="n">
-        <v>3</v>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -10316,8 +10532,10 @@
           <t>00:00:11:07</t>
         </is>
       </c>
-      <c r="J111" t="n">
-        <v>5.2</v>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -10403,8 +10621,10 @@
           <t>00:00:41:02</t>
         </is>
       </c>
-      <c r="J112" t="n">
-        <v>2.1</v>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -10494,8 +10714,10 @@
           <t>00:00:45:02</t>
         </is>
       </c>
-      <c r="J113" t="n">
-        <v>3.4</v>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -10581,8 +10803,10 @@
           <t>00:01:21:02</t>
         </is>
       </c>
-      <c r="J114" t="n">
-        <v>2.1</v>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -10668,8 +10892,10 @@
           <t>00:01:25:07</t>
         </is>
       </c>
-      <c r="J115" t="n">
-        <v>2.1</v>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -10759,8 +10985,10 @@
           <t>00:02:22:00</t>
         </is>
       </c>
-      <c r="J116" t="n">
-        <v>3</v>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -10846,8 +11074,10 @@
           <t>00:02:24:07</t>
         </is>
       </c>
-      <c r="J117" t="n">
-        <v>1.7</v>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -10933,8 +11163,10 @@
           <t>00:02:27:22</t>
         </is>
       </c>
-      <c r="J118" t="n">
-        <v>3</v>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -11020,8 +11252,10 @@
           <t>00:02:32:19</t>
         </is>
       </c>
-      <c r="J119" t="n">
-        <v>4.3</v>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -11107,8 +11341,10 @@
           <t>00:03:37:22</t>
         </is>
       </c>
-      <c r="J120" t="n">
-        <v>3.9</v>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -11194,8 +11430,10 @@
           <t>00:03:43:00</t>
         </is>
       </c>
-      <c r="J121" t="n">
-        <v>3</v>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -11281,8 +11519,10 @@
           <t>00:00:03:02</t>
         </is>
       </c>
-      <c r="J122" t="n">
-        <v>2.1</v>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -11368,8 +11608,10 @@
           <t>00:00:06:17</t>
         </is>
       </c>
-      <c r="J123" t="n">
-        <v>3</v>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
@@ -11455,8 +11697,10 @@
           <t>00:00:09:22</t>
         </is>
       </c>
-      <c r="J124" t="n">
-        <v>2.6</v>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -11542,8 +11786,10 @@
           <t>00:00:15:05</t>
         </is>
       </c>
-      <c r="J125" t="n">
-        <v>4.7</v>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -11629,8 +11875,10 @@
           <t>00:00:42:14</t>
         </is>
       </c>
-      <c r="J126" t="n">
-        <v>5.6</v>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -11716,8 +11964,10 @@
           <t>00:00:46:05</t>
         </is>
       </c>
-      <c r="J127" t="n">
-        <v>3</v>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -11803,8 +12053,10 @@
           <t>00:00:49:19</t>
         </is>
       </c>
-      <c r="J128" t="n">
-        <v>3</v>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -11890,8 +12142,10 @@
           <t>00:00:31:02</t>
         </is>
       </c>
-      <c r="J129" t="n">
-        <v>2.1</v>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -11977,8 +12231,10 @@
           <t>00:00:33:10</t>
         </is>
       </c>
-      <c r="J130" t="n">
-        <v>1.7</v>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
@@ -12068,8 +12324,10 @@
           <t>00:00:33:00</t>
         </is>
       </c>
-      <c r="J131" t="n">
-        <v>1.3</v>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -12159,8 +12417,10 @@
           <t>00:00:56:17</t>
         </is>
       </c>
-      <c r="J132" t="n">
-        <v>1.7</v>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -12250,8 +12510,10 @@
           <t>00:00:59:00</t>
         </is>
       </c>
-      <c r="J133" t="n">
-        <v>1.7</v>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -12337,8 +12599,10 @@
           <t>00:01:01:22</t>
         </is>
       </c>
-      <c r="J134" t="n">
-        <v>0.8</v>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -12424,8 +12688,10 @@
           <t>00:01:05:12</t>
         </is>
       </c>
-      <c r="J135" t="n">
-        <v>3</v>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -12515,8 +12781,10 @@
           <t>00:01:25:07</t>
         </is>
       </c>
-      <c r="J136" t="n">
-        <v>1.3</v>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -12606,8 +12874,10 @@
           <t>00:01:26:14</t>
         </is>
       </c>
-      <c r="J137" t="n">
-        <v>2.6</v>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -12697,8 +12967,10 @@
           <t>00:01:27:00</t>
         </is>
       </c>
-      <c r="J138" t="n">
-        <v>3</v>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -12760,7 +13032,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>19-A (Shot-Bereich 00:00–00:38)</t>
+          <t>19-A</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -12788,8 +13060,10 @@
           <t>00:00:04:10</t>
         </is>
       </c>
-      <c r="J139" t="n">
-        <v>3.4</v>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -12798,7 +13072,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>STIMME</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -12808,12 +13082,12 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Du hast mehr als einen Anfang erlebt.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P139" t="inlineStr"/>
@@ -12824,7 +13098,7 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S139" t="inlineStr"/>
@@ -12847,7 +13121,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>19-A (Shot-Bereich 00:00–00:38)</t>
+          <t>19-A</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -12875,8 +13149,10 @@
           <t>00:00:09:17</t>
         </is>
       </c>
-      <c r="J140" t="n">
-        <v>4.7</v>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -12885,7 +13161,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -12895,12 +13171,12 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>Und jedes Mal dachte ich, das wäre mein einziges Leben.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P140" t="inlineStr"/>
@@ -12911,7 +13187,7 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S140" t="inlineStr"/>
@@ -12934,7 +13210,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>19-B (Shot-Bereich 00:38–01:26)</t>
+          <t>19-B</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -12962,8 +13238,10 @@
           <t>00:00:41:02</t>
         </is>
       </c>
-      <c r="J141" t="n">
-        <v>2.1</v>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -12972,7 +13250,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -12982,12 +13260,12 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>Woher kommt dieser Ort?</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P141" t="inlineStr"/>
@@ -12998,7 +13276,7 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S141" t="inlineStr"/>
@@ -13021,7 +13299,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>19-B (Shot-Bereich 00:38–01:26)</t>
+          <t>19-B</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -13049,8 +13327,10 @@
           <t>00:00:46:10</t>
         </is>
       </c>
-      <c r="J142" t="n">
-        <v>4.7</v>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -13059,7 +13339,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>STIMME</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -13069,12 +13349,12 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Aus dem, was erinnert wurde. Aus den Verbindungen zwischen Leben.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P142" t="inlineStr"/>
@@ -13085,7 +13365,7 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S142" t="inlineStr"/>
@@ -13108,7 +13388,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>19-B (Shot-Bereich 00:38–01:26)</t>
+          <t>19-B</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -13136,8 +13416,10 @@
           <t>00:00:49:02</t>
         </is>
       </c>
-      <c r="J143" t="n">
-        <v>2.1</v>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
@@ -13146,7 +13428,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -13156,12 +13438,12 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Wer hat ihn gebaut?</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P143" t="inlineStr"/>
@@ -13172,7 +13454,7 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S143" t="inlineStr"/>
@@ -13195,7 +13477,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>19-B (Shot-Bereich 00:38–01:26)</t>
+          <t>19-B</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -13223,8 +13505,10 @@
           <t>00:00:51:00</t>
         </is>
       </c>
-      <c r="J144" t="n">
-        <v>1.3</v>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
@@ -13233,7 +13517,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>STIMME</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -13243,12 +13527,12 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Keiner allein.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P144" t="inlineStr"/>
@@ -13259,7 +13543,7 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S144" t="inlineStr"/>
@@ -13282,7 +13566,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>19-C (Shot-Bereich 01:26–02:34)</t>
+          <t>19-C</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -13310,8 +13594,10 @@
           <t>00:01:28:17</t>
         </is>
       </c>
-      <c r="J145" t="n">
-        <v>1.7</v>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
@@ -13320,7 +13606,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -13330,12 +13616,12 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Wer bist du?</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P145" t="inlineStr"/>
@@ -13346,7 +13632,7 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S145" t="inlineStr"/>
@@ -13369,7 +13655,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>19-C (Shot-Bereich 01:26–02:34)</t>
+          <t>19-C</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -13397,8 +13683,10 @@
           <t>00:01:38:14</t>
         </is>
       </c>
-      <c r="J146" t="n">
-        <v>1.3</v>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -13407,7 +13695,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>STIMME A</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -13417,12 +13705,12 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Eine Erinnerung.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P146" t="inlineStr"/>
@@ -13433,7 +13721,7 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S146" t="inlineStr"/>
@@ -13456,7 +13744,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>19-C (Shot-Bereich 01:26–02:34)</t>
+          <t>19-C</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -13484,8 +13772,10 @@
           <t>00:01:40:12</t>
         </is>
       </c>
-      <c r="J147" t="n">
-        <v>1.3</v>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -13494,7 +13784,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>STIMME B</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -13504,12 +13794,12 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Ein Abschied.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P147" t="inlineStr"/>
@@ -13520,7 +13810,7 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S147" t="inlineStr"/>
@@ -13543,7 +13833,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>19-C (Shot-Bereich 01:26–02:34)</t>
+          <t>19-C</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -13571,8 +13861,10 @@
           <t>00:01:43:05</t>
         </is>
       </c>
-      <c r="J148" t="n">
-        <v>2.1</v>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
@@ -13581,7 +13873,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>STIMME C</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -13591,12 +13883,12 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Etwas, das weitergegeben wurde.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P148" t="inlineStr"/>
@@ -13607,12 +13899,12 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>„Etwas, das …“: nach „etwas“ ist „was“ üblicher; „das“ ist umgangssprachlich verbreitet.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
     </row>
@@ -13634,7 +13926,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>19-C (Shot-Bereich 01:26–02:34)</t>
+          <t>19-C</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -13662,8 +13954,10 @@
           <t>00:01:46:10</t>
         </is>
       </c>
-      <c r="J149" t="n">
-        <v>2.6</v>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -13672,7 +13966,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>MEHRERE STIMMEN, NICHT SYNCHRON</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -13682,12 +13976,12 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Wir sind, was geblieben ist.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P149" t="inlineStr"/>
@@ -13698,7 +13992,7 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S149" t="inlineStr"/>
@@ -13721,7 +14015,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>19-D (Shot-Bereich 02:34–03:42)</t>
+          <t>19-D</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -13749,8 +14043,10 @@
           <t>00:02:36:17</t>
         </is>
       </c>
-      <c r="J150" t="n">
-        <v>1.7</v>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -13759,7 +14055,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -13769,12 +14065,12 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Bist du Gott?</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P150" t="inlineStr"/>
@@ -13785,7 +14081,7 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S150" t="inlineStr"/>
@@ -13808,7 +14104,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>19-D (Shot-Bereich 02:34–03:42)</t>
+          <t>19-D</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -13836,8 +14132,10 @@
           <t>00:02:38:02</t>
         </is>
       </c>
-      <c r="J151" t="n">
-        <v>0.8</v>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
@@ -13846,7 +14144,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -13856,12 +14154,12 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Nein.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P151" t="inlineStr"/>
@@ -13872,7 +14170,7 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S151" t="inlineStr"/>
@@ -13895,7 +14193,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>19-D (Shot-Bereich 02:34–03:42)</t>
+          <t>19-D</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -13923,8 +14221,10 @@
           <t>00:02:41:07</t>
         </is>
       </c>
-      <c r="J152" t="n">
-        <v>2.6</v>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
@@ -13933,7 +14233,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -13943,12 +14243,12 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Aber du weißt so viel.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P152" t="inlineStr"/>
@@ -13959,7 +14259,7 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S152" t="inlineStr"/>
@@ -13982,7 +14282,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>19-D (Shot-Bereich 02:34–03:42)</t>
+          <t>19-D</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -14010,8 +14310,10 @@
           <t>00:02:49:17</t>
         </is>
       </c>
-      <c r="J153" t="n">
-        <v>7.8</v>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -14020,7 +14322,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -14030,12 +14332,12 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>Wir wissen, was verbunden ist. Nicht alles, was je war. Und nicht alles, was noch sein wird.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P153" t="inlineStr"/>
@@ -14046,7 +14348,7 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S153" t="inlineStr"/>
@@ -14069,7 +14371,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>19-D (Shot-Bereich 02:34–03:42)</t>
+          <t>19-D</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -14097,8 +14399,10 @@
           <t>00:02:53:07</t>
         </is>
       </c>
-      <c r="J154" t="n">
-        <v>3</v>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -14107,7 +14411,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -14117,12 +14421,12 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Dann kann sich dieses Wissen irren?</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P154" t="inlineStr"/>
@@ -14133,7 +14437,7 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S154" t="inlineStr"/>
@@ -14156,7 +14460,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>19-D (Shot-Bereich 02:34–03:42)</t>
+          <t>19-D</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -14184,8 +14488,10 @@
           <t>00:02:58:05</t>
         </is>
       </c>
-      <c r="J155" t="n">
-        <v>4.3</v>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -14194,7 +14500,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -14204,12 +14510,12 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Ja. Erinnerungen können irren. Deshalb suchen wir nach Zusammenhängen.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P155" t="inlineStr"/>
@@ -14220,7 +14526,7 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S155" t="inlineStr"/>
@@ -14243,7 +14549,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>19-E (Shot-Bereich 03:42–04:38)</t>
+          <t>19-E</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -14271,8 +14577,10 @@
           <t>00:03:46:22</t>
         </is>
       </c>
-      <c r="J156" t="n">
-        <v>3.9</v>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
@@ -14281,7 +14589,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -14291,12 +14599,12 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Lange bevor jemand sich erinnerte, gab es Leben.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P156" t="inlineStr"/>
@@ -14307,7 +14615,7 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S156" t="inlineStr"/>
@@ -14330,7 +14638,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>19-E (Shot-Bereich 03:42–04:38)</t>
+          <t>19-E</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -14358,8 +14666,10 @@
           <t>00:03:53:17</t>
         </is>
       </c>
-      <c r="J157" t="n">
-        <v>4.7</v>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -14368,7 +14678,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -14378,12 +14688,12 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Irgendwann entstanden Wesen, die ihre Welt erfuhren und aufeinander antworteten.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -14394,7 +14704,7 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S157" t="inlineStr"/>
@@ -14417,7 +14727,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>19-E (Shot-Bereich 03:42–04:38)</t>
+          <t>19-E</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14445,8 +14755,10 @@
           <t>00:04:00:19</t>
         </is>
       </c>
-      <c r="J158" t="n">
-        <v>6.5</v>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -14455,7 +14767,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -14465,12 +14777,12 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>Mit ihnen entstanden die ersten Echos – in der Welt, die du hier kennenlernst.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P158" t="inlineStr"/>
@@ -14481,7 +14793,7 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S158" t="inlineStr"/>
@@ -14504,7 +14816,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>19-F (Shot-Bereich 04:38–05:10)</t>
+          <t>19-F</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14532,8 +14844,10 @@
           <t>00:04:42:22</t>
         </is>
       </c>
-      <c r="J159" t="n">
-        <v>3.9</v>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -14542,7 +14856,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -14552,12 +14866,12 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Und was ist mit dem Anfang von allem?</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P159" t="inlineStr"/>
@@ -14568,7 +14882,7 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S159" t="inlineStr"/>
@@ -14591,7 +14905,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>19-F (Shot-Bereich 04:38–05:10)</t>
+          <t>19-F</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14619,8 +14933,10 @@
           <t>00:04:46:02</t>
         </is>
       </c>
-      <c r="J160" t="n">
-        <v>2.6</v>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -14629,7 +14945,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -14639,12 +14955,12 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Diese Antwort haben wir nicht.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P160" t="inlineStr"/>
@@ -14655,7 +14971,7 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S160" t="inlineStr"/>
@@ -14678,7 +14994,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>19-F (Shot-Bereich 04:38–05:10)</t>
+          <t>19-F</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -14706,8 +15022,10 @@
           <t>00:04:51:14</t>
         </is>
       </c>
-      <c r="J161" t="n">
-        <v>3.4</v>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -14716,7 +15034,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -14726,12 +15044,12 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Vielleicht beginnt deine nächste Frage erst dort.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P161" t="inlineStr"/>
@@ -14742,7 +15060,7 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S161" t="inlineStr"/>
@@ -14765,7 +15083,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>20-A (Shot-Bereich 00:00–01:00)</t>
+          <t>20-A</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -14793,8 +15111,10 @@
           <t>00:00:04:00</t>
         </is>
       </c>
-      <c r="J162" t="n">
-        <v>3</v>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -14803,7 +15123,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -14813,12 +15133,12 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Du bist so viele Wege gegangen.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P162" t="inlineStr"/>
@@ -14829,7 +15149,7 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S162" t="inlineStr"/>
@@ -14852,7 +15172,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>20-A (Shot-Bereich 00:00–01:00)</t>
+          <t>20-A</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -14880,8 +15200,10 @@
           <t>00:00:08:22</t>
         </is>
       </c>
-      <c r="J163" t="n">
-        <v>4.3</v>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -14890,7 +15212,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -14900,12 +15222,12 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>Und trotzdem weiß ich nicht, warum ich hier bin.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P163" t="inlineStr"/>
@@ -14916,7 +15238,7 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S163" t="inlineStr"/>
@@ -14939,7 +15261,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>20-A (Shot-Bereich 00:00–01:00)</t>
+          <t>20-A</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -14967,8 +15289,10 @@
           <t>00:00:12:22</t>
         </is>
       </c>
-      <c r="J164" t="n">
-        <v>3.4</v>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -14977,7 +15301,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -14987,12 +15311,12 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Dann sieh dir deinen ersten Abschied an.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P164" t="inlineStr"/>
@@ -15003,7 +15327,7 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S164" t="inlineStr"/>
@@ -15026,7 +15350,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>20-B (Shot-Bereich 01:00–02:15, Reprise 01:07:12–02:07:12)</t>
+          <t>20-B</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -15054,17 +15378,19 @@
           <t>00:01:29:22</t>
         </is>
       </c>
-      <c r="J165" t="n">
-        <v>3.4</v>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>vorläufig/geschätzt; folgt 1:1 aus C00 (+55,5 s)</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>MANN, AUS C00 (ORIGINAL-O-TON)</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -15074,12 +15400,12 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>Glaubst du … ich habe genug getan?</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P165" t="inlineStr"/>
@@ -15090,7 +15416,7 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_001, Zeile 81); Entscheidung 23.10.2026: volle 60 s, alle 8 Zeilen</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S165" t="inlineStr"/>
@@ -15113,7 +15439,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>20-B (Shot-Bereich 01:00–02:15, Reprise 01:07:12–02:07:12)</t>
+          <t>20-B</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -15141,17 +15467,19 @@
           <t>00:01:34:10</t>
         </is>
       </c>
-      <c r="J166" t="n">
-        <v>3.9</v>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>vorläufig/geschätzt; folgt 1:1 aus C00 (+55,5 s)</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>TOCHTER, AUS C00 (ORIGINAL-O-TON)</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -15161,17 +15489,17 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>Ich weiß, dass du vieles anders machen wolltest.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>sucht nicht nach einer beruhigenden Lüge</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
@@ -15181,7 +15509,7 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_002, Zeile 82); Entscheidung 23.10.2026: volle 60 s, alle 8 Zeilen</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S166" t="inlineStr"/>
@@ -15204,7 +15532,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>20-B (Shot-Bereich 01:00–02:15, Reprise 01:07:12–02:07:12)</t>
+          <t>20-B</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -15232,17 +15560,19 @@
           <t>00:01:38:22</t>
         </is>
       </c>
-      <c r="J167" t="n">
-        <v>3.9</v>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>vorläufig/geschätzt; folgt 1:1 aus C00 (+55,5 s)</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>MANN, AUS C00 (ORIGINAL-O-TON)</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -15252,12 +15582,12 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Es gibt so viel, das ich nie …</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P167" t="inlineStr"/>
@@ -15268,12 +15598,12 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_003, Zeile 83); Entscheidung 23.10.2026: volle 60 s, alle 8 Zeilen</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>„so viel, das ich nie …“: nach „viel“ verlangt die Standardsprache „was“ (so viel, was …). Mögliche Absicht der Sprechweise – nicht geändert.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
     </row>
@@ -15295,7 +15625,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>20-B (Shot-Bereich 01:00–02:15, Reprise 01:07:12–02:07:12)</t>
+          <t>20-B</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -15323,17 +15653,19 @@
           <t>00:01:40:19</t>
         </is>
       </c>
-      <c r="J168" t="n">
-        <v>1.3</v>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>vorläufig/geschätzt; folgt 1:1 aus C00 (+55,5 s)</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>TOCHTER, AUS C00 (ORIGINAL-O-TON)</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -15343,12 +15675,12 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>Ich weiß.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P168" t="inlineStr"/>
@@ -15359,7 +15691,7 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_004, Zeile 84); Entscheidung 23.10.2026: volle 60 s, alle 8 Zeilen</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S168" t="inlineStr"/>
@@ -15382,7 +15714,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>20-B (Shot-Bereich 01:00–02:15, Reprise 01:07:12–02:07:12)</t>
+          <t>20-B</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -15410,17 +15742,19 @@
           <t>00:01:44:10</t>
         </is>
       </c>
-      <c r="J169" t="n">
-        <v>3</v>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>vorläufig/geschätzt; folgt 1:1 aus C00 (+55,5 s)</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>MANN, AUS C00 (ORIGINAL-O-TON)</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -15430,12 +15764,12 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Und was, wenn nichts davon bleibt?</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P169" t="inlineStr"/>
@@ -15446,7 +15780,7 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_005, Zeile 85); Entscheidung 23.10.2026: volle 60 s, alle 8 Zeilen</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S169" t="inlineStr"/>
@@ -15469,7 +15803,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>20-B (Shot-Bereich 01:00–02:15, Reprise 01:07:12–02:07:12)</t>
+          <t>20-B</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -15497,17 +15831,19 @@
           <t>00:01:51:02</t>
         </is>
       </c>
-      <c r="J170" t="n">
-        <v>6.1</v>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>vorläufig/geschätzt; folgt 1:1 aus C00 (+55,5 s)</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>TOCHTER, AUS C00 (ORIGINAL-O-TON)</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -15517,12 +15853,12 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>Manche Dinge bleiben bei den Menschen. Auch wenn man es selbst nie erfährt.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P170" t="inlineStr"/>
@@ -15533,7 +15869,7 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_006, Zeile 86); Entscheidung 23.10.2026: volle 60 s, alle 8 Zeilen</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S170" t="inlineStr"/>
@@ -15556,7 +15892,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>20-B (Shot-Bereich 01:00–02:15, Reprise 01:07:12–02:07:12)</t>
+          <t>20-B</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -15584,17 +15920,19 @@
           <t>00:01:53:19</t>
         </is>
       </c>
-      <c r="J171" t="n">
-        <v>2.1</v>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>vorläufig/geschätzt; folgt 1:1 aus C00 (+55,5 s)</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>MANN, AUS C00 (ORIGINAL-O-TON)</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -15604,12 +15942,12 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Das weiß ich nicht.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P171" t="inlineStr"/>
@@ -15620,7 +15958,7 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_007, Zeile 87); Entscheidung 23.10.2026: volle 60 s, alle 8 Zeilen</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S171" t="inlineStr"/>
@@ -15643,7 +15981,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>20-B (Shot-Bereich 01:00–02:15, Reprise 01:07:12–02:07:12)</t>
+          <t>20-B</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -15671,17 +16009,19 @@
           <t>00:01:58:17</t>
         </is>
       </c>
-      <c r="J172" t="n">
-        <v>4.3</v>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>vorläufig/geschätzt; folgt 1:1 aus C00 (+55,5 s)</t>
+          <t>vorläufig/geschätzt</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>TOCHTER, AUS C00 (ORIGINAL-O-TON)</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -15691,12 +16031,12 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>Du musst es jetzt nicht wissen. Ich bin hier.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P172" t="inlineStr"/>
@@ -15707,7 +16047,7 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt; Reprise aus C00, Originalton – keine Neuaufnahme (Quelle VO_C00_008, Zeile 88); Entscheidung 23.10.2026: volle 60 s, alle 8 Zeilen</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S172" t="inlineStr"/>
@@ -15730,7 +16070,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>20-C (Shot-Bereich 02:15–03:35)</t>
+          <t>20-C</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -15758,8 +16098,10 @@
           <t>00:02:18:14</t>
         </is>
       </c>
-      <c r="J173" t="n">
-        <v>2.6</v>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -15768,7 +16110,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -15778,12 +16120,12 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Das … war mein Leben?</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P173" t="inlineStr"/>
@@ -15794,7 +16136,7 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S173" t="inlineStr"/>
@@ -15817,7 +16159,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>20-C (Shot-Bereich 02:15–03:35)</t>
+          <t>20-C</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -15845,8 +16187,10 @@
           <t>00:02:23:22</t>
         </is>
       </c>
-      <c r="J174" t="n">
-        <v>4.7</v>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -15855,7 +16199,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -15865,12 +16209,12 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Ein Leben vor den deinen. Dasselbe Echo. Nicht derselbe Mensch.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P174" t="inlineStr"/>
@@ -15881,7 +16225,7 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S174" t="inlineStr"/>
@@ -15904,7 +16248,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>20-C (Shot-Bereich 02:15–03:35)</t>
+          <t>20-C</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -15932,8 +16276,10 @@
           <t>00:02:27:12</t>
         </is>
       </c>
-      <c r="J175" t="n">
-        <v>3</v>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -15942,7 +16288,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -15952,12 +16298,12 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Aber ich erinnere mich nicht daran.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P175" t="inlineStr"/>
@@ -15968,7 +16314,7 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S175" t="inlineStr"/>
@@ -15991,7 +16337,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>20-C (Shot-Bereich 02:15–03:35)</t>
+          <t>20-C</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -16019,8 +16365,10 @@
           <t>00:02:32:10</t>
         </is>
       </c>
-      <c r="J176" t="n">
-        <v>4.3</v>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -16029,7 +16377,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -16039,12 +16387,12 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Weil ein neues Leben ein eigenes Leben sein muss.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P176" t="inlineStr"/>
@@ -16055,7 +16403,7 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S176" t="inlineStr"/>
@@ -16078,7 +16426,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>20-C (Shot-Bereich 02:15–03:35)</t>
+          <t>20-C</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -16106,8 +16454,10 @@
           <t>00:02:34:17</t>
         </is>
       </c>
-      <c r="J177" t="n">
-        <v>1.7</v>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
@@ -16116,7 +16466,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -16126,12 +16476,12 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>Und seine Tochter?</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P177" t="inlineStr"/>
@@ -16142,7 +16492,7 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S177" t="inlineStr"/>
@@ -16165,7 +16515,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>20-C (Shot-Bereich 02:15–03:35)</t>
+          <t>20-C</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -16193,8 +16543,10 @@
           <t>00:02:40:22</t>
         </is>
       </c>
-      <c r="J178" t="n">
-        <v>5.6</v>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -16203,7 +16555,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -16213,12 +16565,12 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>Sie hatte ihr Leben. Ihre Geschichte ging weiter. Sie gehört nicht dir.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P178" t="inlineStr"/>
@@ -16229,7 +16581,7 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S178" t="inlineStr"/>
@@ -16252,7 +16604,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>20-D (Shot-Bereich 03:35–05:05)</t>
+          <t>20-D</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -16280,8 +16632,10 @@
           <t>00:03:42:22</t>
         </is>
       </c>
-      <c r="J179" t="n">
-        <v>6.9</v>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -16290,7 +16644,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -16300,12 +16654,12 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>Er wollte wissen, ob er genug getan hatte. Und ich stelle mir die gleiche Frage.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P179" t="inlineStr"/>
@@ -16316,12 +16670,12 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>„die gleiche Frage“ – gemeint ist dieselbe Frage; stilistisch, in Alltagssprache akzeptiert.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
     </row>
@@ -16343,7 +16697,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>20-D (Shot-Bereich 03:35–05:05)</t>
+          <t>20-D</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -16371,8 +16725,10 @@
           <t>00:03:47:19</t>
         </is>
       </c>
-      <c r="J180" t="n">
-        <v>4.3</v>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -16381,7 +16737,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -16391,12 +16747,12 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>Kein Leben lässt sich auf eine einzige Zahl reduzieren.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P180" t="inlineStr"/>
@@ -16407,7 +16763,7 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S180" t="inlineStr"/>
@@ -16430,7 +16786,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>20-D (Shot-Bereich 03:35–05:05)</t>
+          <t>20-D</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -16458,8 +16814,10 @@
           <t>00:03:51:00</t>
         </is>
       </c>
-      <c r="J181" t="n">
-        <v>2.6</v>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -16468,7 +16826,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -16478,12 +16836,12 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>Aber ich habe andere verändert.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P181" t="inlineStr"/>
@@ -16494,7 +16852,7 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S181" t="inlineStr"/>
@@ -16517,7 +16875,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>20-D (Shot-Bereich 03:35–05:05)</t>
+          <t>20-D</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -16545,8 +16903,10 @@
           <t>00:03:54:05</t>
         </is>
       </c>
-      <c r="J182" t="n">
-        <v>2.6</v>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -16555,7 +16915,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -16565,12 +16925,12 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>Und sie haben dich verändert.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P182" t="inlineStr"/>
@@ -16581,7 +16941,7 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S182" t="inlineStr"/>
@@ -16604,7 +16964,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>20-D (Shot-Bereich 03:35–05:05)</t>
+          <t>20-D</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -16632,8 +16992,10 @@
           <t>00:03:59:02</t>
         </is>
       </c>
-      <c r="J183" t="n">
-        <v>4.3</v>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -16642,7 +17004,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -16652,12 +17014,12 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>Dann gibt es keinen Weg, alles richtig zu machen?</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P183" t="inlineStr"/>
@@ -16668,7 +17030,7 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S183" t="inlineStr"/>
@@ -16691,7 +17053,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>20-D (Shot-Bereich 03:35–05:05)</t>
+          <t>20-D</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -16719,8 +17081,10 @@
           <t>00:04:02:17</t>
         </is>
       </c>
-      <c r="J184" t="n">
-        <v>3</v>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -16729,7 +17093,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
@@ -16739,12 +17103,12 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>Es gibt Verantwortung. Keine vollständige Kontrolle.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P184" t="inlineStr"/>
@@ -16755,7 +17119,7 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S184" t="inlineStr"/>
@@ -16778,7 +17142,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>20-E (Shot-Bereich 05:05–06:32)</t>
+          <t>20-E</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -16806,8 +17170,10 @@
           <t>00:05:09:00</t>
         </is>
       </c>
-      <c r="J185" t="n">
-        <v>3</v>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -16816,7 +17182,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -16826,12 +17192,12 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>Wer hat dann diese Welt erschaffen?</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P185" t="inlineStr"/>
@@ -16842,7 +17208,7 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S185" t="inlineStr"/>
@@ -16865,7 +17231,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>20-E (Shot-Bereich 05:05–06:32)</t>
+          <t>20-E</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -16893,8 +17259,10 @@
           <t>00:05:12:14</t>
         </is>
       </c>
-      <c r="J186" t="n">
-        <v>3</v>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -16903,7 +17271,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -16913,12 +17281,12 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Den ersten Ursprung kennen wir nicht.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P186" t="inlineStr"/>
@@ -16929,7 +17297,7 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S186" t="inlineStr"/>
@@ -16952,7 +17320,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>20-E (Shot-Bereich 05:05–06:32)</t>
+          <t>20-E</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -16980,8 +17348,10 @@
           <t>00:05:24:05</t>
         </is>
       </c>
-      <c r="J187" t="n">
-        <v>9.5</v>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
@@ -16990,7 +17360,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -17000,12 +17370,12 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>Aber die Welt, in der Menschen leben – ihre Häuser, Geschichten, Hoffnungen, ihre Wunden und ihre Möglichkeiten – formen sie miteinander.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P187" t="inlineStr"/>
@@ -17016,7 +17386,7 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S187" t="inlineStr"/>
@@ -17039,7 +17409,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>20-E (Shot-Bereich 05:05–06:32)</t>
+          <t>20-E</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -17067,8 +17437,10 @@
           <t>00:05:26:02</t>
         </is>
       </c>
-      <c r="J188" t="n">
-        <v>1.3</v>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -17077,7 +17449,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -17087,12 +17459,12 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>Wir alle?</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P188" t="inlineStr"/>
@@ -17103,7 +17475,7 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S188" t="inlineStr"/>
@@ -17126,7 +17498,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20-E (Shot-Bereich 05:05–06:32)</t>
+          <t>20-E</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -17154,8 +17526,10 @@
           <t>00:05:33:14</t>
         </is>
       </c>
-      <c r="J189" t="n">
-        <v>6.9</v>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -17164,7 +17538,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -17174,12 +17548,12 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>Mit jedem Leben. Mit dem, was wir tun. Und mit dem, was wir anderen ermöglichen.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P189" t="inlineStr"/>
@@ -17190,7 +17564,7 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S189" t="inlineStr"/>
@@ -17213,7 +17587,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>20-F (Shot-Bereich 06:32–07:40)</t>
+          <t>20-F</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -17241,8 +17615,10 @@
           <t>00:06:35:02</t>
         </is>
       </c>
-      <c r="J190" t="n">
-        <v>2.1</v>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -17251,7 +17627,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
@@ -17261,12 +17637,12 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Sind wir die Schöpfer?</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P190" t="inlineStr"/>
@@ -17277,7 +17653,7 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S190" t="inlineStr"/>
@@ -17300,7 +17676,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>20-F (Shot-Bereich 06:32–07:40)</t>
+          <t>20-F</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -17328,8 +17704,10 @@
           <t>00:06:40:22</t>
         </is>
       </c>
-      <c r="J191" t="n">
-        <v>5.2</v>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -17338,7 +17716,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -17348,12 +17726,12 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>Wir sind Mitgestalter. Keiner von uns besitzt das Leben eines anderen.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P191" t="inlineStr"/>
@@ -17364,7 +17742,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S191" t="inlineStr"/>
@@ -17387,7 +17765,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>20-F (Shot-Bereich 06:32–07:40)</t>
+          <t>20-F</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -17415,8 +17793,10 @@
           <t>00:06:43:05</t>
         </is>
       </c>
-      <c r="J192" t="n">
-        <v>1.7</v>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -17425,7 +17805,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -17435,12 +17815,12 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>Und das hier?</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P192" t="inlineStr"/>
@@ -17451,7 +17831,7 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S192" t="inlineStr"/>
@@ -17474,7 +17854,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>20-F (Shot-Bereich 06:32–07:40)</t>
+          <t>20-F</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -17502,8 +17882,10 @@
           <t>00:06:51:14</t>
         </is>
       </c>
-      <c r="J193" t="n">
-        <v>7.8</v>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -17512,7 +17894,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
@@ -17522,12 +17904,12 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>Eine Möglichkeit, Bedingungen für eine neue Welt zu schaffen. Das Leben darin wird seinen eigenen Weg finden.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P193" t="inlineStr"/>
@@ -17538,7 +17920,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S193" t="inlineStr"/>
@@ -17561,7 +17943,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>20-G (Shot-Bereich 07:40–09:00)</t>
+          <t>20-G</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -17589,8 +17971,10 @@
           <t>00:07:46:05</t>
         </is>
       </c>
-      <c r="J194" t="n">
-        <v>5.2</v>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -17599,7 +17983,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -17609,12 +17993,12 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>Wenn ich mich entscheide … weiß ich dann, was daraus wird?</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P194" t="inlineStr"/>
@@ -17625,7 +18009,7 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S194" t="inlineStr"/>
@@ -17648,7 +18032,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>20-G (Shot-Bereich 07:40–09:00)</t>
+          <t>20-G</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -17676,8 +18060,10 @@
           <t>00:07:47:14</t>
         </is>
       </c>
-      <c r="J195" t="n">
-        <v>0.8</v>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
@@ -17686,7 +18072,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -17696,12 +18082,12 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Nein.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P195" t="inlineStr"/>
@@ -17712,7 +18098,7 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S195" t="inlineStr"/>
@@ -17735,7 +18121,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>20-G (Shot-Bereich 07:40–09:00)</t>
+          <t>20-G</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -17763,8 +18149,10 @@
           <t>00:07:50:19</t>
         </is>
       </c>
-      <c r="J196" t="n">
-        <v>2.6</v>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
@@ -17773,7 +18161,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -17783,12 +18171,12 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>Dann kann ich Fehler machen.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P196" t="inlineStr"/>
@@ -17799,7 +18187,7 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S196" t="inlineStr"/>
@@ -17822,7 +18210,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>20-G (Shot-Bereich 07:40–09:00)</t>
+          <t>20-G</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -17850,8 +18238,10 @@
           <t>00:07:52:05</t>
         </is>
       </c>
-      <c r="J197" t="n">
-        <v>0.8</v>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -17860,7 +18250,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -17870,12 +18260,12 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>Ja.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P197" t="inlineStr"/>
@@ -17886,7 +18276,7 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S197" t="inlineStr"/>
@@ -17909,7 +18299,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>20-G (Shot-Bereich 07:40–09:00)</t>
+          <t>20-G</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -17937,8 +18327,10 @@
           <t>00:07:55:10</t>
         </is>
       </c>
-      <c r="J198" t="n">
-        <v>2.6</v>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
@@ -17947,7 +18339,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>SPIELER-ECHO</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -17957,12 +18349,12 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>Und trotzdem darf ich anfangen?</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P198" t="inlineStr"/>
@@ -17973,7 +18365,7 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S198" t="inlineStr"/>
@@ -17996,7 +18388,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>20-G (Shot-Bereich 07:40–09:00)</t>
+          <t>20-G</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -18024,8 +18416,10 @@
           <t>00:07:58:14</t>
         </is>
       </c>
-      <c r="J199" t="n">
-        <v>2.6</v>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -18034,7 +18428,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>STIMMEN</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -18044,12 +18438,12 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>Du darfst mitgestalten. Nicht herrschen.</t>
+          <t>[INTERN – nicht im öffentlichen Repo]</t>
         </is>
       </c>
       <c r="P199" t="inlineStr"/>
@@ -18060,7 +18454,7 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>Zeitcode vorläufig/geschätzt</t>
+          <t>Inhalt intern</t>
         </is>
       </c>
       <c r="S199" t="inlineStr"/>
@@ -18111,8 +18505,10 @@
           <t>00:02:29:22</t>
         </is>
       </c>
-      <c r="J200" t="n">
-        <v>3.9</v>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
@@ -18202,8 +18598,10 @@
           <t>00:02:34:02</t>
         </is>
       </c>
-      <c r="J201" t="n">
-        <v>2.1</v>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -18244,7 +18642,6 @@
       <c r="S201" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>